--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_2_5.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_2_5.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="135" windowWidth="14805" windowHeight="7980"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14355" windowHeight="4920"/>
   </bookViews>
   <sheets>
     <sheet name="表2-5企业债券按行业、企业" sheetId="4" r:id="rId1"/>
@@ -16,7 +16,7 @@
     <definedName name="Err">[1]综合校验!$B$2</definedName>
     <definedName name="Thd">[1]综合校验!$B$1</definedName>
   </definedNames>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -197,9 +197,6 @@
   </si>
   <si>
     <t>列编号</t>
-  </si>
-  <si>
-    <t>单位：万元</t>
   </si>
   <si>
     <t>01-银行非保本理财</t>
@@ -228,6 +225,7 @@
         <b/>
         <sz val="16"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>5</t>
@@ -237,6 +235,7 @@
         <b/>
         <sz val="16"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 企业债券分行业、企业规模统计模板</t>
@@ -568,6 +567,10 @@
   </si>
   <si>
     <t>${report.enddate}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：万元</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -579,7 +582,7 @@
     <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="180" formatCode="#,##0.000000_ "/>
+    <numFmt numFmtId="179" formatCode="#,##0.000000_ "/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -592,32 +595,38 @@
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -643,6 +652,7 @@
       <b/>
       <sz val="16"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -809,7 +819,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -857,7 +867,7 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -900,6 +910,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -994,7 +1007,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1036,7 +1049,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1071,7 +1084,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1294,7 +1307,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="24" customFormat="1" ht="24.95" customHeight="1">
       <c r="A1" s="43" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
@@ -1309,10 +1322,10 @@
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
       <c r="D2" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F2" s="19"/>
       <c r="G2" s="19"/>
@@ -1320,32 +1333,32 @@
     </row>
     <row r="3" spans="1:8" s="20" customFormat="1" ht="24.95" customHeight="1">
       <c r="A3" s="23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="21" t="s">
         <v>167</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>168</v>
       </c>
       <c r="F3" s="22"/>
       <c r="G3" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24.95" customHeight="1" thickBot="1">
       <c r="A4" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C4" s="44"/>
       <c r="D4" s="36"/>
@@ -1353,7 +1366,7 @@
       <c r="F4" s="37"/>
       <c r="G4" s="38"/>
       <c r="H4" s="39" t="s">
-        <v>57</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="17.100000000000001" customHeight="1">
@@ -1411,19 +1424,19 @@
       </c>
       <c r="C7" s="48"/>
       <c r="D7" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.100000000000001" customHeight="1">
@@ -1435,19 +1448,19 @@
       </c>
       <c r="C8" s="42"/>
       <c r="D8" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="17.100000000000001" customHeight="1">
@@ -1459,19 +1472,19 @@
       </c>
       <c r="C9" s="42"/>
       <c r="D9" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H9" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="17.100000000000001" customHeight="1">
@@ -1483,19 +1496,19 @@
       </c>
       <c r="C10" s="42"/>
       <c r="D10" s="25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="17.100000000000001" customHeight="1">
@@ -1507,19 +1520,19 @@
       </c>
       <c r="C11" s="42"/>
       <c r="D11" s="25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H11" s="25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="17.100000000000001" customHeight="1">
@@ -1531,19 +1544,19 @@
       </c>
       <c r="C12" s="42"/>
       <c r="D12" s="25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H12" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="17.100000000000001" customHeight="1">
@@ -1555,19 +1568,19 @@
       </c>
       <c r="C13" s="42"/>
       <c r="D13" s="25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="17.100000000000001" customHeight="1">
@@ -1579,19 +1592,19 @@
       </c>
       <c r="C14" s="42"/>
       <c r="D14" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H14" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="17.100000000000001" customHeight="1">
@@ -1603,19 +1616,19 @@
       </c>
       <c r="C15" s="42"/>
       <c r="D15" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G15" s="25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H15" s="25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="17.100000000000001" customHeight="1">
@@ -1627,19 +1640,19 @@
       </c>
       <c r="C16" s="42"/>
       <c r="D16" s="25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H16" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="17.100000000000001" customHeight="1">
@@ -1651,19 +1664,19 @@
       </c>
       <c r="C17" s="42"/>
       <c r="D17" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G17" s="25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H17" s="25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="17.100000000000001" customHeight="1">
@@ -1675,19 +1688,19 @@
       </c>
       <c r="C18" s="42"/>
       <c r="D18" s="25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H18" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="17.100000000000001" customHeight="1">
@@ -1699,19 +1712,19 @@
       </c>
       <c r="C19" s="42"/>
       <c r="D19" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H19" s="25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="17.100000000000001" customHeight="1">
@@ -1723,19 +1736,19 @@
       </c>
       <c r="C20" s="42"/>
       <c r="D20" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="17.100000000000001" customHeight="1">
@@ -1747,19 +1760,19 @@
       </c>
       <c r="C21" s="42"/>
       <c r="D21" s="25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="17.100000000000001" customHeight="1">
@@ -1771,19 +1784,19 @@
       </c>
       <c r="C22" s="42"/>
       <c r="D22" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G22" s="25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H22" s="25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="17.100000000000001" customHeight="1">
@@ -1795,19 +1808,19 @@
       </c>
       <c r="C23" s="42"/>
       <c r="D23" s="25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G23" s="25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H23" s="25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="17.100000000000001" customHeight="1">
@@ -1819,19 +1832,19 @@
       </c>
       <c r="C24" s="42"/>
       <c r="D24" s="25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G24" s="25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H24" s="25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="17.100000000000001" customHeight="1">
@@ -1843,19 +1856,19 @@
       </c>
       <c r="C25" s="42"/>
       <c r="D25" s="25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G25" s="25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H25" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15" thickBot="1">
@@ -1867,19 +1880,19 @@
       </c>
       <c r="C26" s="50"/>
       <c r="D26" s="41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E26" s="41" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F26" s="41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G26" s="41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H26" s="41" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="73.5" customHeight="1">
@@ -1899,21 +1912,21 @@
         <v>2</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="11" t="s">
         <v>1</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F28" s="11"/>
       <c r="G28" s="10" t="s">
         <v>0</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1924,7 +1937,13 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B21:C21"/>
@@ -1933,13 +1952,6 @@
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B4:C4"/>
@@ -1949,6 +1961,7 @@
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="2">
